--- a/development/02 fatigue delamination/AP5MEF104_Fatigue.xlsx
+++ b/development/02 fatigue delamination/AP5MEF104_Fatigue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 Projekt\01 UP4foundry\02 Arbeitsphase\04 MethodEntwicklungphase\Interface Study\AP5MEF04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49056AF-825B-4C3C-81A3-589176C2EEAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70750EA6-6686-440E-93CB-040B57884BC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" xr2:uid="{C7235D5C-96EC-45E2-9C6F-6CF1FAF5FCC0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{C7235D5C-96EC-45E2-9C6F-6CF1FAF5FCC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1482,11 +1482,11 @@
         <v>12.25</v>
       </c>
       <c r="S14" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="2"/>
-        <v>1.4100000000000001</v>
+        <v>2.8200000000000003</v>
       </c>
       <c r="U14" s="1">
         <v>55000</v>
@@ -1551,11 +1551,11 @@
         <v>13.439999999999998</v>
       </c>
       <c r="S15" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="2"/>
-        <v>3.3499999999999979</v>
+        <v>6.6999999999999957</v>
       </c>
       <c r="U15" s="1">
         <v>55000</v>
@@ -1620,11 +1620,11 @@
         <v>23.51</v>
       </c>
       <c r="S16" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="2"/>
-        <v>7.8300000000000018</v>
+        <v>15.660000000000004</v>
       </c>
       <c r="U16" s="1">
         <v>55000</v>
@@ -1689,11 +1689,11 @@
         <v>45.533000000000001</v>
       </c>
       <c r="S17" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="2"/>
-        <v>3.1630000000000038</v>
+        <v>6.3260000000000076</v>
       </c>
       <c r="U17" s="1">
         <v>55000</v>
